--- a/data/gravel/Tumbleweed Stargazer 2025.xlsx
+++ b/data/gravel/Tumbleweed Stargazer 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/hardtail/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82885803-3C4A-6D44-9B9D-BCA3476D81A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B80690E-0651-EE41-9035-D6F3C6072DEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3140" yWindow="2180" windowWidth="25900" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2900" yWindow="2180" windowWidth="25900" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/data/gravel/Tumbleweed Stargazer 2025.xlsx
+++ b/data/gravel/Tumbleweed Stargazer 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B80690E-0651-EE41-9035-D6F3C6072DEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FAD3BAB-BCE9-B24F-A0BD-57360AA77D8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2900" yWindow="2180" windowWidth="25900" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="103">
   <si>
     <t>brand</t>
   </si>
@@ -44,9 +44,6 @@
     <t>model</t>
   </si>
   <si>
-    <t xml:space="preserve">Stargazer </t>
-  </si>
-  <si>
     <t>model_year</t>
   </si>
   <si>
@@ -339,6 +336,12 @@
   </si>
   <si>
     <t>usd</t>
+  </si>
+  <si>
+    <t>https://tumbleweed.cc/cdn/shop/files/stargazer-award_587dd612-0320-4843-ab87-11f3858dc7ef.jpg?v=1756404775&amp;width=1000</t>
+  </si>
+  <si>
+    <t>Stargazer (Gen 1)</t>
   </si>
 </sst>
 </file>
@@ -696,13 +699,13 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
-        <v>3</v>
+      <c r="B2" s="1" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3">
         <v>2025</v>
@@ -710,7 +713,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4" s="2">
         <v>45885</v>
@@ -718,49 +721,54 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>96</v>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
         <v>7</v>
-      </c>
-      <c r="B7" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
         <v>9</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>10</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>11</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>12</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>13</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>14</v>
-      </c>
-      <c r="G8" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
         <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
       </c>
       <c r="C9">
         <v>535</v>
@@ -780,10 +788,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
         <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
       </c>
       <c r="C10">
         <v>73.5</v>
@@ -803,10 +811,10 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
         <v>20</v>
-      </c>
-      <c r="B11" t="s">
-        <v>21</v>
       </c>
       <c r="C11">
         <v>380</v>
@@ -826,10 +834,10 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
         <v>22</v>
-      </c>
-      <c r="B12" t="s">
-        <v>23</v>
       </c>
       <c r="C12">
         <v>115</v>
@@ -849,10 +857,10 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" t="s">
         <v>24</v>
-      </c>
-      <c r="B13" t="s">
-        <v>25</v>
       </c>
       <c r="C13">
         <v>69</v>
@@ -872,10 +880,10 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s">
         <v>27</v>
-      </c>
-      <c r="B14" t="s">
-        <v>28</v>
       </c>
       <c r="C14">
         <v>55</v>
@@ -895,10 +903,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" t="s">
         <v>29</v>
-      </c>
-      <c r="B15" t="s">
-        <v>30</v>
       </c>
       <c r="C15">
         <v>450</v>
@@ -918,10 +926,10 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s">
         <v>31</v>
-      </c>
-      <c r="B16" t="s">
-        <v>32</v>
       </c>
       <c r="C16">
         <v>63.5</v>
@@ -941,10 +949,10 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" t="s">
         <v>33</v>
-      </c>
-      <c r="B17" t="s">
-        <v>34</v>
       </c>
       <c r="C17">
         <v>574</v>
@@ -964,10 +972,10 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" t="s">
         <v>35</v>
-      </c>
-      <c r="B18" t="s">
-        <v>36</v>
       </c>
       <c r="C18">
         <v>365</v>
@@ -987,10 +995,10 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" t="s">
         <v>37</v>
-      </c>
-      <c r="B19" t="s">
-        <v>38</v>
       </c>
       <c r="C19">
         <v>750</v>
@@ -1010,10 +1018,10 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C20">
         <v>440</v>
@@ -1033,39 +1041,39 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" t="s">
         <v>39</v>
-      </c>
-      <c r="B21" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D25">
         <v>2300</v>
@@ -1073,10 +1081,10 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C26">
         <v>29</v>
@@ -1096,10 +1104,10 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C27">
         <v>59.69</v>
@@ -1119,10 +1127,10 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B28" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C28">
         <v>66.040000000000006</v>
@@ -1142,73 +1150,73 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>47</v>
+      </c>
+      <c r="B29" t="s">
         <v>48</v>
-      </c>
-      <c r="B29" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>49</v>
+      </c>
+      <c r="B30" t="s">
         <v>50</v>
-      </c>
-      <c r="B30" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>51</v>
+      </c>
+      <c r="B32" t="s">
         <v>52</v>
-      </c>
-      <c r="B32" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>89</v>
+      </c>
+      <c r="B33" t="s">
         <v>90</v>
-      </c>
-      <c r="B33" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>91</v>
+      </c>
+      <c r="B34" t="s">
         <v>92</v>
-      </c>
-      <c r="B34" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>93</v>
+      </c>
+      <c r="B35" t="s">
         <v>94</v>
-      </c>
-      <c r="B35" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>53</v>
+      </c>
+      <c r="B36" t="s">
         <v>54</v>
-      </c>
-      <c r="B36" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B39">
         <f>2.6*25.4</f>
@@ -1217,7 +1225,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B40">
         <v>3</v>
@@ -1225,27 +1233,27 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B45">
         <v>148</v>
@@ -1253,7 +1261,7 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B46">
         <v>110</v>
@@ -1261,20 +1269,20 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B49">
         <v>27.2</v>
@@ -1282,15 +1290,15 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B51">
         <v>38</v>
@@ -1298,12 +1306,12 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B53">
         <v>180</v>
@@ -1311,7 +1319,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B54">
         <v>180</v>
@@ -1319,35 +1327,35 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B60">
         <v>3</v>
@@ -1355,46 +1363,46 @@
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B67">
         <v>1350</v>
@@ -1402,7 +1410,7 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B68">
         <v>4150</v>
@@ -1410,15 +1418,15 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Tumbleweed Stargazer 2025.xlsx
+++ b/data/gravel/Tumbleweed Stargazer 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FAD3BAB-BCE9-B24F-A0BD-57360AA77D8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A4522EF-F280-7440-9784-1663AD8E5A6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2900" yWindow="2180" windowWidth="25900" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="105">
   <si>
     <t>brand</t>
   </si>
@@ -335,13 +335,19 @@
     <t>no</t>
   </si>
   <si>
-    <t>usd</t>
-  </si>
-  <si>
     <t>https://tumbleweed.cc/cdn/shop/files/stargazer-award_587dd612-0320-4843-ab87-11f3858dc7ef.jpg?v=1756404775&amp;width=1000</t>
   </si>
   <si>
     <t>Stargazer (Gen 1)</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Garden City, Idaho, USA</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
@@ -681,7 +687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -700,7 +706,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -729,7 +735,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -1426,7 +1432,15 @@
         <v>88</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Tumbleweed Stargazer 2025.xlsx
+++ b/data/gravel/Tumbleweed Stargazer 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A4522EF-F280-7440-9784-1663AD8E5A6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EB2D432-9CEE-E94C-AA16-5F8939E968DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2900" yWindow="2180" windowWidth="25900" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="111">
   <si>
     <t>brand</t>
   </si>
@@ -348,6 +348,24 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -687,7 +705,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1275,171 +1293,201 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>65</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>67</v>
-      </c>
-      <c r="B49">
-        <v>27.2</v>
+        <v>107</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>68</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>69</v>
-      </c>
-      <c r="B51">
-        <v>38</v>
+        <v>109</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>70</v>
+        <v>110</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>71</v>
-      </c>
-      <c r="B53">
-        <v>180</v>
+        <v>65</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>72</v>
-      </c>
-      <c r="B54">
-        <v>180</v>
+        <v>66</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>73</v>
+        <v>67</v>
+      </c>
+      <c r="B55">
+        <v>27.2</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>74</v>
+        <v>68</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>75</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>98</v>
+        <v>69</v>
+      </c>
+      <c r="B57">
+        <v>38</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>77</v>
+        <v>71</v>
+      </c>
+      <c r="B59">
+        <v>180</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B60">
-        <v>3</v>
+        <v>180</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>81</v>
+        <v>75</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>82</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>83</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>84</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>96</v>
+        <v>78</v>
+      </c>
+      <c r="B66">
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>85</v>
-      </c>
-      <c r="B67">
-        <v>1350</v>
+        <v>79</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>86</v>
-      </c>
-      <c r="B68">
-        <v>4150</v>
+        <v>80</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
+        <v>82</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>83</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>84</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>85</v>
+      </c>
+      <c r="B73">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>86</v>
+      </c>
+      <c r="B74">
+        <v>4150</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
         <v>88</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B76" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71" s="1" t="s">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="B77" s="1" t="s">
         <v>103</v>
       </c>
     </row>
